--- a/consent_forms/044_par_q_fitness_form_gbpt--consent_forms.xlsx
+++ b/consent_forms/044_par_q_fitness_form_gbpt--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Has the patient ever had any of the following?</t>
+          <t>Do you have any medical conditions that may impact your physical activity?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>What is your current age?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>patient_weight</t>
+          <t>height</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>What is your height (in meters)?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>What is your weight (in kg)?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bmi</t>
+          <t>What is your body mass index (BMI)?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>blood pressure</t>
+          <t>What is your blood pressure?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>What is your resting heart rate?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>previous_injuries</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>Have you ever had any previous injuries or illnesses that may impact your exercise routine?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>blood_pressure</t>
+          <t>exercise_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>blood pressure</t>
+          <t>What is your exercise frequency (days per week)?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>exercise_type</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>How often do you exercise?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>exercise_session_duration</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>How long do you exercise each session?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>exercise_location</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>resting_heart_rate</t>
+          <t>Do you exercise at home or in a gym?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>exercise_frequency</t>
+          <t>exercise_buddy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>exercise_frequency</t>
+          <t>Who is your exercise buddy?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>exercise</t>
+          <t>medical_equipment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>exercise</t>
+          <t>Do you have any medical equipment for exercise?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>exercise_frequency</t>
+          <t>future_exercise_plans</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>exercise_frequency</t>
+          <t>Do you have any plans for future exercise plans?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,62 +865,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>exercise</t>
+          <t>exercise_type_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>exercise</t>
+          <t>How do you usually exercise?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>exercise</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>exercise</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>exercise</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>exercise</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -937,10 +891,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -965,255 +919,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>previous_injuries_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>previous_injuries_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>exercise_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>exercise_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>exercise_session_duration_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>exercise_session_duration_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>exercise_location_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>exercise_location_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>exercise_buddy_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>exercise_buddy_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>medical_equipment_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>medical_equipment_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>exercise_choices</t>
+          <t>future_exercise_plans_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>future_exercise_plans_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>exercise_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>exercise_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Option B</t>
         </is>
       </c>
     </row>
